--- a/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
+++ b/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2600,8 +2600,220 @@
       <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>c382929d69fa4230</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.8799519807923168</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0.871287</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>-0.1054839807923168</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:15:59.035187Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>3251419577f94543</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.8799519807923168</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>0.871287</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>-0.1054839807923168</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:53:25.832875Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ19"/>
+  <autoFilter ref="A1:AJ21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
+++ b/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ21"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2812,8 +2812,326 @@
       <c r="AI21" s="2" t="inlineStr"/>
       <c r="AJ21" s="2" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ab7428738d3f4bdb</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.8799519807923168</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0.871287</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>-0.1054839807923168</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:58:47.415615Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>9a6badfe25684a95</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.8799519807923168</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>0.871287</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>-0.1054839807923168</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:04:30.174342Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>cf18b56979d842b3</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.8799519807923168</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>0.871287</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>-0.1054839807923168</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:23:15.869749Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ21"/>
+  <autoFilter ref="A1:AJ24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
+++ b/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ24"/>
+  <dimension ref="A1:AJ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3130,8 +3130,1398 @@
       <c r="AI24" s="2" t="inlineStr"/>
       <c r="AJ24" s="2" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>c102a533b3484816</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.8799519807923168</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>0.871287</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>-0.1054839807923168</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T15:00:50.549281Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>f6b57bb8a3fb467a</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.8699609882964889</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>0.861386</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>-0.09549298829648889</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T16:50:21.446994Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>35249e6a2c894ecc</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.8599439775910364</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>0.851485</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>-0.08547597759103631</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:05:21.116275Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>5b12c8bc1e8e49e8</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.8599439775910364</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0.851485</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>-0.08547597759103631</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:35.240301Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>40d76566f75b4a4a</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>fb46ae94639bf9af</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>401857114</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.774468</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.8599439775910364</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>0.851485</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>-0.08547597759103631</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T01:07:13.594446Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0.3257</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:21:25.465340Z</t>
+        </is>
+      </c>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>3964b9feeee64b29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>db4cf2e6209fa446</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>401857115</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.660664</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>0.653465</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.00080005442176867</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:15.540830Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>841279db88a74b19</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>cbc087f3d2f12e27</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>401857116</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.741322</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.7899159663865546</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>0.782178</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>-0.048593966386554555</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:16.652644Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ca9e8252f7604031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>72f5694b0619f905</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>401857117</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.532764</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>0.584158</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>-0.05739993442622948</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:17.483570Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>21be12d234934532</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>5cc21b269728431d</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>401857118</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.549529</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>0.554455</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>-0.009942365638766493</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:23:19.363696Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>490174a9e89a4b6d</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>db4cf2e6209fa446</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>401857115</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.660664</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>0.653465</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.00080005442176867</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:03.119408Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>1b684a33c5f04f0f</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>cbc087f3d2f12e27</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>401857116</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.741322</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.7899159663865546</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>0.782178</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>-0.048593966386554555</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:04.100169Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>295bf66d2c5149a8</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>72f5694b0619f905</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>401857117</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.532764</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>0.584158</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>-0.05739993442622948</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:04.826877Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>4c95530a7a6e4522</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>5cc21b269728431d</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>401857118</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.549529</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>0.554455</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>-0.009942365638766493</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:34:05.642651Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ24"/>
+  <autoFilter ref="A1:AJ37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
+++ b/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ37"/>
+  <dimension ref="A1:AJ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4520,8 +4520,856 @@
       <c r="AI37" s="2" t="inlineStr"/>
       <c r="AJ37" s="2" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>43531467f18e4c4e</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>db4cf2e6209fa446</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>401857115</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.660664</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>0.653465</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0.00080005442176867</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:19:00.769700Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>bc59bcf4466b4605</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>cbc087f3d2f12e27</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>401857116</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.741322</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.7701149425287357</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>0.762376</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>-0.028792942528735654</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:19:02.010000Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>d30ea1240d594960</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>72f5694b0619f905</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>401857117</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.532764</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>0.584158</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>-0.05739993442622948</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:19:02.517727Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>32bfb81ae4034b5e</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>5cc21b269728431d</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>401857118</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.549529</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>0.554455</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>-0.009942365638766493</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:19:03.268344Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>71903506819a483b</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>db4cf2e6209fa446</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>401857115</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.660664</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.6598639455782314</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>0.653465</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.00080005442176867</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:33.816980Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>8eefe32e656e4edd</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>cbc087f3d2f12e27</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>401857116</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.741322</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.7701149425287357</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>0.762376</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>-0.028792942528735654</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:34.422318Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>af07ac91040a4dd2</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>72f5694b0619f905</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>401857117</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.532764</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>0.564356</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>-0.038051450643776796</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:34.867255Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>9431056b618b47a2</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>5cc21b269728431d</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>401857118</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.549529</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.5708154506437768</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>0.564356</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>-0.021286450643776766</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:35.451044Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:00-0400</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ37"/>
+  <autoFilter ref="A1:AJ45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
+++ b/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ45"/>
+  <dimension ref="A1:AJ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5368,8 +5368,432 @@
       <c r="AI45" s="2" t="inlineStr"/>
       <c r="AJ45" s="2" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>fab7f1114d9b4227</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>7527e38cbf3d298e</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>401857123</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.561972</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>0.386139</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.17134700000000003</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:02:29.181440Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>f2fbf146c1f3404c</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>7527e38cbf3d298e</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>401857123</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.561972</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>0.386139</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>0.17134700000000003</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:08:44.734712Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>1c1dffbe991143cb</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>7527e38cbf3d298e</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>401857123</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.561972</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.3597122302158273</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>0.356436</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.2022597697841727</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T12:14:45.698076Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>911401b17a614fbb</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>7527e38cbf3d298e</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>401857123</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.561972</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>0.336634</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.22183594557823133</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:39.610102Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ45"/>
+  <autoFilter ref="A1:AJ49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
+++ b/data/main/model_ledgers/wnba-moneyline-elo-trend-lr.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ49"/>
+  <dimension ref="A1:AJ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5792,8 +5792,114 @@
       <c r="AI49" s="2" t="inlineStr"/>
       <c r="AJ49" s="2" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>393f501e7b3a46d8</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>wnba-moneyline-elo-trend-lr</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>7afd5274214b58b7efd7f7febc7be3ab33b92351cda5cc6403c0a39faea0cc8c</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>wnba-elo-trend-lr-v4</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>7527e38cbf3d298e</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>401857123</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.561972</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.3401360544217687</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>0.336634</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>0.22183594557823133</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:28:03.051036Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07T19:30:00-0400</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ49"/>
+  <autoFilter ref="A1:AJ50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>